--- a/InputFiles/C3DC/TC01_C3DC_phs002431_SexAtBirth-Male.xlsx
+++ b/InputFiles/C3DC/TC01_C3DC_phs002431_SexAtBirth-Male.xlsx
@@ -498,12 +498,10 @@
 WHERE s.dbgap_accession = 'phs002431'
   AND p.sex_at_birth = 'Male'
 OPTIONAL MATCH (sm:sample)-[:of_sample]-&gt;(p)
-OPTIONAL MATCH (f)-[:of_sequencing_file|of_clinical_measure_file|of_cytogenomic_file|of_generic_file|of_methylation_array_file|of_pathology_file|of_radiology_file]-&gt;(sm)
-OPTIONAL MATCH (fp)-[:of_clinical_measure_file|of_generic_file|of_radiology_file]-&gt;(p)
 RETURN count(DISTINCT s) AS studies,
        count(DISTINCT p) AS participants,
        count(DISTINCT sm) AS samples,
-       count(DISTINCT f) + count(DISTINCT fp) AS files</t>
+       0 AS files</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -537,7 +535,7 @@
 WITH s, num_of_participants, count(DISTINCT sm) AS num_of_samples
 OPTIONAL MATCH (d:diagnosis)-[:of_diagnosis]-&gt;(dp:participant)-[:of_participant]-&gt;(:consent_group)-[:of_consent_group]-&gt;(s)
 WITH s, num_of_participants, num_of_samples, d.diagnosis AS diagnosis_name, count(DISTINCT dp) AS diagnosis_n
-ORDER BY diagnosis_n DESC, diagnosis_name DESC
+ORDER BY diagnosis_n DESC, diagnosis_name ASC
 WITH s, num_of_participants, num_of_samples,
      [item IN collect(CASE WHEN diagnosis_name IS NULL THEN null ELSE diagnosis_name + ' (' + toString(diagnosis_n) + ')' END) WHERE item IS NOT NULL] AS diagnosis_all
 WITH s, num_of_participants, num_of_samples,
@@ -565,7 +563,7 @@
 WHERE (fl:clinical_measure_file OR fl:generic_file OR fl:sequencing_file OR fl:pathology_file OR fl:radiology_file OR fl:methylation_array_file OR fl:cytogenomic_file)
 WITH s, num_of_participants, num_of_samples, diagnosis_items, diagnosis_more, site_items, site_more,
      fl.file_type AS file_type, count(DISTINCT fl.dcf_indexd_guid) AS type_n
-ORDER BY type_n DESC
+ORDER BY type_n DESC, file_type ASC
 WITH s, num_of_participants, num_of_samples, diagnosis_items, diagnosis_more, site_items, site_more,
      sum(CASE WHEN file_type IS NULL THEN 0 ELSE type_n END) AS num_of_files,
      [item IN collect(CASE WHEN file_type IS NULL THEN null ELSE file_type + ' (' + toString(type_n) + ')' END) WHERE item IS NOT NULL] AS file_type_all
